--- a/학습리포트.xlsx
+++ b/학습리포트.xlsx
@@ -20,8 +20,7 @@
     <sheet name="2026-04-18" sheetId="15" r:id="rId15"/>
     <sheet name="2026-04-21" sheetId="16" r:id="rId16"/>
     <sheet name="2026-04-25" sheetId="17" r:id="rId17"/>
-    <sheet name="이월과제" sheetId="18" r:id="rId18"/>
-    <sheet name="설정" sheetId="19" r:id="rId19"/>
+    <sheet name="설정" sheetId="18" r:id="rId18"/>
   </sheets>
 </workbook>
 </file>
@@ -712,7 +711,7 @@
         <v/>
       </c>
     </row>
-    <row r="11">
+    <row r="11" xml:space="preserve">
       <c r="A11" t="str">
         <v>2724584323</v>
       </c>
@@ -725,8 +724,9 @@
       <c r="D11" t="str">
         <v>방정식과 부등식</v>
       </c>
-      <c r="E11" t="str">
-        <v>6. 이차방정식과 이차함수 p.82-86</v>
+      <c r="E11" t="str" xml:space="preserve">
+        <v xml:space="preserve">6. 이차방정식과 이차함수 p.82-86
+3. 복소수 p.45-52</v>
       </c>
       <c r="F11" t="str">
         <v>숙제 p.82-86</v>
@@ -758,7 +758,7 @@
         <v>4. 복소수 p.45-52</v>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>숙제 p.45-51</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -770,7 +770,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" xml:space="preserve">
+    <row r="13">
       <c r="A13" t="str">
         <v>2724582000</v>
       </c>
@@ -781,11 +781,10 @@
         <v>풍산자 라이트유형</v>
       </c>
       <c r="D13" t="str">
-        <v>방정식과 부등식</v>
-      </c>
-      <c r="E13" t="str" xml:space="preserve">
-        <v xml:space="preserve">5. 이차방정식 p.64-68
-6. 이차방정식과 이차함수 p.75-77</v>
+        <v>전 범위 복습</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -811,7 +810,7 @@
         <v>풍산자 라이트유형</v>
       </c>
       <c r="D14" t="str">
-        <v>방정식과 부등식</v>
+        <v>전 범위 복습</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -840,7 +839,7 @@
         <v>풍산자 라이트유형</v>
       </c>
       <c r="D15" t="str">
-        <v>방정식과 부등식</v>
+        <v>전 범위 복습</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -869,7 +868,7 @@
         <v>풍산자 라이트유형</v>
       </c>
       <c r="D16" t="str">
-        <v>방정식과 부등식</v>
+        <v>전 범위 복습</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -898,7 +897,7 @@
         <v>풍산자 라이트유형</v>
       </c>
       <c r="D17" t="str">
-        <v>방정식과 부등식</v>
+        <v>전 범위 복습</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -925,7 +924,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:I7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -953,12 +952,6 @@
         <v>과제4</v>
       </c>
       <c r="I1" t="str">
-        <v>추가과제1</v>
-      </c>
-      <c r="J1" t="str">
-        <v>추가과제2</v>
-      </c>
-      <c r="K1" t="str">
         <v>비고</v>
       </c>
     </row>
@@ -988,12 +981,6 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>숙제 p.64-67 (유형 09~12)</v>
-      </c>
-      <c r="J2" t="str">
-        <v>숙제 p.75-77</v>
-      </c>
-      <c r="K2" t="str">
         <v/>
       </c>
     </row>
@@ -1023,12 +1010,6 @@
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>p. 75-77 안한부분</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
         <v/>
       </c>
     </row>
@@ -1058,12 +1039,6 @@
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>숙제 p.64-67 (유형 09~12) 안한 부분</v>
-      </c>
-      <c r="J4" t="str">
-        <v>숙제 p.75-77</v>
-      </c>
-      <c r="K4" t="str">
         <v/>
       </c>
     </row>
@@ -1095,12 +1070,6 @@
       <c r="I5" t="str">
         <v/>
       </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -1130,12 +1099,6 @@
       <c r="I6" t="str">
         <v/>
       </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -1163,25 +1126,19 @@
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>p. 75-77 안한부분</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:K7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1209,6 +1166,12 @@
         <v>과제4</v>
       </c>
       <c r="I1" t="str">
+        <v>추가과제1</v>
+      </c>
+      <c r="J1" t="str">
+        <v>추가과제2</v>
+      </c>
+      <c r="K1" t="str">
         <v>비고</v>
       </c>
     </row>
@@ -1240,25 +1203,31 @@
       <c r="I2" t="str">
         <v/>
       </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
         <v>김도은</v>
       </c>
-      <c r="B3" t="str">
-        <v/>
+      <c r="B3">
+        <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
+        <v>1번, 3번, 4번, 5-4</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>2</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>2</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -1268,34 +1237,46 @@
       </c>
       <c r="I3" t="str">
         <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v>[이월] 숙제 p.75-77 (03.31 출제) → 완료</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v>서윤희</v>
       </c>
-      <c r="B4" t="str">
-        <v/>
+      <c r="B4">
+        <v>2</v>
       </c>
       <c r="C4" t="str">
         <v/>
       </c>
-      <c r="D4" t="str">
-        <v/>
+      <c r="D4">
+        <v>10</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>0</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H4" t="str">
         <v/>
       </c>
       <c r="I4" t="str">
+        <v>저번 시험 풀어보기</v>
+      </c>
+      <c r="J4" t="str">
+        <v>이차방정식 프린트 1번,3번,5번</v>
+      </c>
+      <c r="K4" t="str">
         <v/>
       </c>
     </row>
@@ -1303,17 +1284,17 @@
       <c r="A5" t="str">
         <v>황선재</v>
       </c>
-      <c r="B5" t="str">
-        <v/>
+      <c r="B5">
+        <v>2</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>3번, 4번,5번</v>
       </c>
       <c r="D5" t="str">
         <v/>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>0</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -1325,6 +1306,12 @@
         <v/>
       </c>
       <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
         <v/>
       </c>
     </row>
@@ -1332,49 +1319,55 @@
       <c r="A6" t="str">
         <v>인원빈</v>
       </c>
-      <c r="B6" t="str">
-        <v/>
+      <c r="B6">
+        <v>2</v>
       </c>
       <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6" t="str">
-        <v/>
+        <v>3번,5-4</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>0</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>0</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>0</v>
       </c>
       <c r="H6" t="str">
         <v/>
       </c>
       <c r="I6" t="str">
         <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v>[이월] 숙제 p.64-67 (유형 09~12) (03.31 출제) → 미완료, [이월] 숙제 p.75-77 (03.31 출제) → 미완료</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v>김희은</v>
       </c>
-      <c r="B7" t="str">
-        <v/>
+      <c r="B7">
+        <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v/>
+        <v>1번, 5-3</v>
+      </c>
+      <c r="D7">
+        <v>90</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -1383,12 +1376,18 @@
         <v/>
       </c>
       <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1430,17 +1429,17 @@
       <c r="A2" t="str">
         <v>유하정</v>
       </c>
-      <c r="B2" t="str">
-        <v/>
+      <c r="B2">
+        <v>2</v>
       </c>
       <c r="C2" t="str">
         <v/>
       </c>
-      <c r="D2" t="str">
-        <v/>
+      <c r="D2">
+        <v>100</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>0</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -1459,17 +1458,17 @@
       <c r="A3" t="str">
         <v>김도은</v>
       </c>
-      <c r="B3" t="str">
-        <v/>
+      <c r="B3">
+        <v>2</v>
       </c>
       <c r="C3" t="str">
         <v/>
       </c>
-      <c r="D3" t="str">
-        <v/>
+      <c r="D3">
+        <v>80</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -1488,17 +1487,17 @@
       <c r="A4" t="str">
         <v>서윤희</v>
       </c>
-      <c r="B4" t="str">
-        <v/>
+      <c r="B4">
+        <v>2</v>
       </c>
       <c r="C4" t="str">
         <v/>
       </c>
-      <c r="D4" t="str">
-        <v/>
+      <c r="D4">
+        <v>10</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>0</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -1507,7 +1506,7 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>0</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -1546,17 +1545,17 @@
       <c r="A6" t="str">
         <v>인원빈</v>
       </c>
-      <c r="B6" t="str">
-        <v/>
+      <c r="B6">
+        <v>2</v>
       </c>
       <c r="C6" t="str">
         <v/>
       </c>
-      <c r="D6" t="str">
-        <v/>
+      <c r="D6">
+        <v>10</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>0</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -1609,7 +1608,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1637,6 +1636,15 @@
         <v>과제4</v>
       </c>
       <c r="I1" t="str">
+        <v>추가과제1</v>
+      </c>
+      <c r="J1" t="str">
+        <v>추가과제2</v>
+      </c>
+      <c r="K1" t="str">
+        <v>추가과제3</v>
+      </c>
+      <c r="L1" t="str">
         <v>비고</v>
       </c>
     </row>
@@ -1644,17 +1652,17 @@
       <c r="A2" t="str">
         <v>유하정</v>
       </c>
-      <c r="B2" t="str">
-        <v/>
+      <c r="B2">
+        <v>2</v>
       </c>
       <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v/>
+        <v>51번,53번,31-3,31-4, 27번</v>
+      </c>
+      <c r="D2">
+        <v>50</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -1666,6 +1674,15 @@
         <v/>
       </c>
       <c r="I2" t="str">
+        <v>숙제 p.61-63</v>
+      </c>
+      <c r="J2" t="str">
+        <v>숙제 p.59-60 고치기 &amp; 풀기</v>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
         <v/>
       </c>
     </row>
@@ -1673,17 +1690,17 @@
       <c r="A3" t="str">
         <v>김도은</v>
       </c>
-      <c r="B3" t="str">
-        <v/>
+      <c r="B3">
+        <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
+        <v>51번, 53번, 16번, 31-2, 31-3</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>2</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -1695,6 +1712,15 @@
         <v/>
       </c>
       <c r="I3" t="str">
+        <v>숙제 p.61-63</v>
+      </c>
+      <c r="J3" t="str">
+        <v>숙제 p.45-51 부분 고치기</v>
+      </c>
+      <c r="K3" t="str">
+        <v>숙제 p.59-60 고치기 &amp; 풀기</v>
+      </c>
+      <c r="L3" t="str">
         <v/>
       </c>
     </row>
@@ -1702,17 +1728,17 @@
       <c r="A4" t="str">
         <v>서윤희</v>
       </c>
-      <c r="B4" t="str">
-        <v/>
+      <c r="B4">
+        <v>2</v>
       </c>
       <c r="C4" t="str">
         <v/>
       </c>
-      <c r="D4" t="str">
-        <v/>
+      <c r="D4">
+        <v>10</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>0</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -1724,6 +1750,15 @@
         <v/>
       </c>
       <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
         <v/>
       </c>
     </row>
@@ -1755,22 +1790,31 @@
       <c r="I5" t="str">
         <v/>
       </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v>인원빈</v>
       </c>
-      <c r="B6" t="str">
-        <v/>
+      <c r="B6">
+        <v>2</v>
       </c>
       <c r="C6" t="str">
         <v/>
       </c>
-      <c r="D6" t="str">
-        <v/>
+      <c r="D6">
+        <v>10</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>0</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -1782,6 +1826,15 @@
         <v/>
       </c>
       <c r="I6" t="str">
+        <v>p.58-59 (프린트물)</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
         <v/>
       </c>
     </row>
@@ -1789,17 +1842,17 @@
       <c r="A7" t="str">
         <v>김희은</v>
       </c>
-      <c r="B7" t="str">
-        <v/>
+      <c r="B7">
+        <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v/>
+        <v>51번,53번,31번,27번</v>
+      </c>
+      <c r="D7">
+        <v>100</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>2</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -1811,12 +1864,21 @@
         <v/>
       </c>
       <c r="I7" t="str">
+        <v>숙제 p.61-63</v>
+      </c>
+      <c r="J7" t="str">
+        <v>숙제 p.45-51 부분 고치기</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2679,983 +2741,6 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D69"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>학생</v>
-      </c>
-      <c r="B1" t="str">
-        <v>확인날짜</v>
-      </c>
-      <c r="C1" t="str">
-        <v>참조</v>
-      </c>
-      <c r="D1" t="str">
-        <v>상태</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>▼ 2026년 3월 10일 (화)</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>김도은</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="C3" t="str">
-        <v>4758948383-과제1</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>김도은</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="C4" t="str">
-        <v>4758948383-과제2</v>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>서윤희</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="C5" t="str">
-        <v>4758948383-과제1</v>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>서윤희</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="C6" t="str">
-        <v>4758948383-과제2</v>
-      </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>황선재</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="C7" t="str">
-        <v>4758948383-과제1</v>
-      </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>황선재</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="C8" t="str">
-        <v>4758948383-과제2</v>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>인원빈</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="C9" t="str">
-        <v>4758948383-과제1</v>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>인원빈</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="C10" t="str">
-        <v>4758948383-과제2</v>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>▼ 2026년 3월 14일 (토)</v>
-      </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>김도은</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-03-14</v>
-      </c>
-      <c r="C12" t="str">
-        <v>1950117256-과제1</v>
-      </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>서윤희</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-03-14</v>
-      </c>
-      <c r="C13" t="str">
-        <v>1950117256-과제1</v>
-      </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>황선재</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-03-14</v>
-      </c>
-      <c r="C14" t="str">
-        <v>1950117256-과제1</v>
-      </c>
-      <c r="D14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>인원빈</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2026-03-14</v>
-      </c>
-      <c r="C15" t="str">
-        <v>1950117256-과제1</v>
-      </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>▼ 2026년 3월 17일 (화)</v>
-      </c>
-      <c r="B16" t="str">
-        <v/>
-      </c>
-      <c r="C16" t="str">
-        <v/>
-      </c>
-      <c r="D16" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>김도은</v>
-      </c>
-      <c r="B17" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="C17" t="str">
-        <v>3621036327-과제1</v>
-      </c>
-      <c r="D17" t="str">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>서윤희</v>
-      </c>
-      <c r="B18" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="C18" t="str">
-        <v>3621036327-과제2</v>
-      </c>
-      <c r="D18" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>황선재</v>
-      </c>
-      <c r="B19" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="C19" t="str">
-        <v>3621036327-과제2</v>
-      </c>
-      <c r="D19" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>▼ 2026년 3월 21일 (토)</v>
-      </c>
-      <c r="B20" t="str">
-        <v/>
-      </c>
-      <c r="C20" t="str">
-        <v/>
-      </c>
-      <c r="D20" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>김도은</v>
-      </c>
-      <c r="B21" t="str">
-        <v>2026-03-21</v>
-      </c>
-      <c r="C21" t="str">
-        <v>1787141169-과제1</v>
-      </c>
-      <c r="D21" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>김도은</v>
-      </c>
-      <c r="B22" t="str">
-        <v>2026-03-21</v>
-      </c>
-      <c r="C22" t="str">
-        <v>1787141169-과제3</v>
-      </c>
-      <c r="D22" t="str">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>서윤희</v>
-      </c>
-      <c r="B23" t="str">
-        <v>2026-03-21</v>
-      </c>
-      <c r="C23" t="str">
-        <v>1787141169-과제1</v>
-      </c>
-      <c r="D23" t="str">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>서윤희</v>
-      </c>
-      <c r="B24" t="str">
-        <v>2026-03-21</v>
-      </c>
-      <c r="C24" t="str">
-        <v>1787141169-과제2</v>
-      </c>
-      <c r="D24" t="str">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>서윤희</v>
-      </c>
-      <c r="B25" t="str">
-        <v>2026-03-21</v>
-      </c>
-      <c r="C25" t="str">
-        <v>1787141169-과제3</v>
-      </c>
-      <c r="D25" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>황선재</v>
-      </c>
-      <c r="B26" t="str">
-        <v>2026-03-21</v>
-      </c>
-      <c r="C26" t="str">
-        <v>1787141169-과제3</v>
-      </c>
-      <c r="D26" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>황선재</v>
-      </c>
-      <c r="B27" t="str">
-        <v>2026-03-21</v>
-      </c>
-      <c r="C27" t="str">
-        <v>1787141169-과제1</v>
-      </c>
-      <c r="D27" t="str">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>황선재</v>
-      </c>
-      <c r="B28" t="str">
-        <v>2026-03-21</v>
-      </c>
-      <c r="C28" t="str">
-        <v>1787141169-과제2</v>
-      </c>
-      <c r="D28" t="str">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>인원빈</v>
-      </c>
-      <c r="B29" t="str">
-        <v>2026-03-21</v>
-      </c>
-      <c r="C29" t="str">
-        <v>1787141169-과제1</v>
-      </c>
-      <c r="D29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>인원빈</v>
-      </c>
-      <c r="B30" t="str">
-        <v>2026-03-21</v>
-      </c>
-      <c r="C30" t="str">
-        <v>1787141169-과제3</v>
-      </c>
-      <c r="D30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>▼ 2026년 3월 24일 (화)</v>
-      </c>
-      <c r="B31" t="str">
-        <v/>
-      </c>
-      <c r="C31" t="str">
-        <v/>
-      </c>
-      <c r="D31" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>유하정</v>
-      </c>
-      <c r="B32" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="C32" t="str">
-        <v>9467650539-과제1</v>
-      </c>
-      <c r="D32" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>김도은</v>
-      </c>
-      <c r="B33" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="C33" t="str">
-        <v>1787141169-과제1</v>
-      </c>
-      <c r="D33" t="str">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>서윤희</v>
-      </c>
-      <c r="B34" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="C34" t="str">
-        <v>1787141169-과제3</v>
-      </c>
-      <c r="D34" t="str">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>황선재</v>
-      </c>
-      <c r="B35" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="C35" t="str">
-        <v>9467650539-과제1</v>
-      </c>
-      <c r="D35" t="str">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>황선재</v>
-      </c>
-      <c r="B36" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="C36" t="str">
-        <v>1787141169-과제1</v>
-      </c>
-      <c r="D36" t="str">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>황선재</v>
-      </c>
-      <c r="B37" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="C37" t="str">
-        <v>1787141169-과제2</v>
-      </c>
-      <c r="D37" t="str">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>황선재</v>
-      </c>
-      <c r="B38" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="C38" t="str">
-        <v>1787141169-과제3</v>
-      </c>
-      <c r="D38" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>인원빈</v>
-      </c>
-      <c r="B39" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="C39" t="str">
-        <v>9467650539-과제1</v>
-      </c>
-      <c r="D39" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>김희은</v>
-      </c>
-      <c r="B40" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="C40" t="str">
-        <v>9467650539-과제1</v>
-      </c>
-      <c r="D40" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>▼ 2026년 3월 26일 (목)</v>
-      </c>
-      <c r="B41" t="str">
-        <v/>
-      </c>
-      <c r="C41" t="str">
-        <v/>
-      </c>
-      <c r="D41" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>유하정</v>
-      </c>
-      <c r="B42" t="str">
-        <v>2026-03-26</v>
-      </c>
-      <c r="C42" t="str">
-        <v>1328083508-과제1</v>
-      </c>
-      <c r="D42" t="str">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>유하정</v>
-      </c>
-      <c r="B43" t="str">
-        <v>2026-03-26</v>
-      </c>
-      <c r="C43" t="str">
-        <v>9467650539-과제1</v>
-      </c>
-      <c r="D43" t="str">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>김도은</v>
-      </c>
-      <c r="B44" t="str">
-        <v>2026-03-26</v>
-      </c>
-      <c r="C44" t="str">
-        <v>1328083508-과제1</v>
-      </c>
-      <c r="D44" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>서윤희</v>
-      </c>
-      <c r="B45" t="str">
-        <v>2026-03-26</v>
-      </c>
-      <c r="C45" t="str">
-        <v>1328083508-과제1</v>
-      </c>
-      <c r="D45" t="str">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>서윤희</v>
-      </c>
-      <c r="B46" t="str">
-        <v>2026-03-26</v>
-      </c>
-      <c r="C46" t="str">
-        <v>1787141169-과제3</v>
-      </c>
-      <c r="D46" t="str">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>황선재</v>
-      </c>
-      <c r="B47" t="str">
-        <v>2026-03-26</v>
-      </c>
-      <c r="C47" t="str">
-        <v>1328083508-과제1</v>
-      </c>
-      <c r="D47" t="str">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>황선재</v>
-      </c>
-      <c r="B48" t="str">
-        <v>2026-03-26</v>
-      </c>
-      <c r="C48" t="str">
-        <v>1787141169-과제1</v>
-      </c>
-      <c r="D48" t="str">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>황선재</v>
-      </c>
-      <c r="B49" t="str">
-        <v>2026-03-26</v>
-      </c>
-      <c r="C49" t="str">
-        <v>1787141169-과제2</v>
-      </c>
-      <c r="D49" t="str">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>황선재</v>
-      </c>
-      <c r="B50" t="str">
-        <v>2026-03-26</v>
-      </c>
-      <c r="C50" t="str">
-        <v>1787141169-과제3</v>
-      </c>
-      <c r="D50" t="str">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>인원빈</v>
-      </c>
-      <c r="B51" t="str">
-        <v>2026-03-26</v>
-      </c>
-      <c r="C51" t="str">
-        <v>1328083508-과제1</v>
-      </c>
-      <c r="D51" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>▼ 2026년 3월 31일 (화)</v>
-      </c>
-      <c r="B52" t="str">
-        <v/>
-      </c>
-      <c r="C52" t="str">
-        <v/>
-      </c>
-      <c r="D52" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>유하정</v>
-      </c>
-      <c r="B53" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="C53" t="str">
-        <v>1328083508-과제1</v>
-      </c>
-      <c r="D53" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>유하정</v>
-      </c>
-      <c r="B54" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="C54" t="str">
-        <v>9467650539-과제1</v>
-      </c>
-      <c r="D54" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>서윤희</v>
-      </c>
-      <c r="B55" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="C55" t="str">
-        <v>1328083508-과제1</v>
-      </c>
-      <c r="D55" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v>서윤희</v>
-      </c>
-      <c r="B56" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="C56" t="str">
-        <v>1787141169-과제3</v>
-      </c>
-      <c r="D56" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v>황선재</v>
-      </c>
-      <c r="B57" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="C57" t="str">
-        <v>1328083508-과제1</v>
-      </c>
-      <c r="D57" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>황선재</v>
-      </c>
-      <c r="B58" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="C58" t="str">
-        <v>1787141169-과제1</v>
-      </c>
-      <c r="D58" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>황선재</v>
-      </c>
-      <c r="B59" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="C59" t="str">
-        <v>1787141169-과제2</v>
-      </c>
-      <c r="D59" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>황선재</v>
-      </c>
-      <c r="B60" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="C60" t="str">
-        <v>1787141169-과제3</v>
-      </c>
-      <c r="D60" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>▼ 2026년 4월 4일 (토)</v>
-      </c>
-      <c r="B61" t="str">
-        <v/>
-      </c>
-      <c r="C61" t="str">
-        <v/>
-      </c>
-      <c r="D61" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>유하정</v>
-      </c>
-      <c r="B62" t="str">
-        <v>2026-04-04</v>
-      </c>
-      <c r="C62" t="str">
-        <v>9490242494-과제1</v>
-      </c>
-      <c r="D62" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>유하정</v>
-      </c>
-      <c r="B63" t="str">
-        <v>2026-04-04</v>
-      </c>
-      <c r="C63" t="str">
-        <v>9490242494-과제2</v>
-      </c>
-      <c r="D63" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>김도은</v>
-      </c>
-      <c r="B64" t="str">
-        <v>2026-04-04</v>
-      </c>
-      <c r="C64" t="str">
-        <v>9490242494-과제2</v>
-      </c>
-      <c r="D64" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v>서윤희</v>
-      </c>
-      <c r="B65" t="str">
-        <v>2026-04-04</v>
-      </c>
-      <c r="C65" t="str">
-        <v>9490242494-과제1</v>
-      </c>
-      <c r="D65" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v>서윤희</v>
-      </c>
-      <c r="B66" t="str">
-        <v>2026-04-04</v>
-      </c>
-      <c r="C66" t="str">
-        <v>9490242494-과제2</v>
-      </c>
-      <c r="D66" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v>인원빈</v>
-      </c>
-      <c r="B67" t="str">
-        <v>2026-04-04</v>
-      </c>
-      <c r="C67" t="str">
-        <v>9490242494-과제1</v>
-      </c>
-      <c r="D67" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v>인원빈</v>
-      </c>
-      <c r="B68" t="str">
-        <v>2026-04-04</v>
-      </c>
-      <c r="C68" t="str">
-        <v>9490242494-과제2</v>
-      </c>
-      <c r="D68" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>김희은</v>
-      </c>
-      <c r="B69" t="str">
-        <v>2026-04-04</v>
-      </c>
-      <c r="C69" t="str">
-        <v>9490242494-과제2</v>
-      </c>
-      <c r="D69" t="str">
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D69"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C20"/>
   <sheetData>
     <row r="1">
@@ -3872,7 +2957,7 @@
         <v>lastSaved</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-03-31 20:52:48</v>
+        <v>2026-04-14 12:45:58</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -4401,7 +3486,7 @@
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>[이월] 숙제 p.9-14 (03.07 출제) → 완료 | [이월] 숙제 p.9-14 (03.03 출제) → 완료, [이월] 숙제 p.17-19 (03.03 출제) → 완료</v>
+        <v>[이월] 숙제 p.9-14 (03.03 출제) → 완료, [이월] 숙제 p.17-19 (03.03 출제) → 완료</v>
       </c>
     </row>
     <row r="4">
@@ -4829,7 +3914,7 @@
         <v>2</v>
       </c>
       <c r="I3" t="str">
-        <v>[이월] 숙제 p.15-16 (03.14 출제) → 완료 | [이월] 숙제 p.15-16 (03.10 출제) → 완료</v>
+        <v>[이월] 숙제 p.15-16 (03.10 출제) → 완료</v>
       </c>
     </row>
     <row r="4">
@@ -5043,7 +4128,7 @@
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>[이월] 숙제 p.31-33 (03.17 출제) → 완료 | [이월] 숙제 p.31-33 (03.14 출제) → 완료</v>
+        <v>[이월] 숙제 p.31-33 (03.14 출제) → 완료</v>
       </c>
     </row>
     <row r="4">
@@ -5072,7 +4157,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="str">
-        <v>[이월] 숙제 p.22-23 (03.17 출제) → 완료, [이월] 숙제 p.27 (03.17 출제) → 완료, [이월] 숙제 p.31-33 (03.17 출제) → 일부 완료 | [이월] 숙제 p.22-23 (03.14 출제) → 완료, [이월] 숙제 p.27 (03.14 출제) → 완료, [이월] 숙제 p.31-33 (03.14 출제) → 일부 완료</v>
+        <v>[이월] 숙제 p.22-23 (03.14 출제) → 완료, [이월] 숙제 p.27 (03.14 출제) → 완료, [이월] 숙제 p.31-33 (03.14 출제) → 일부 완료</v>
       </c>
     </row>
     <row r="5">
@@ -5257,7 +4342,7 @@
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>[이월] 숙제 p.22-23 (03.17 출제) → 완료 | [이월] 숙제 p.22-23 (03.14 출제) → 완료</v>
+        <v>[이월] 숙제 p.22-23 (03.14 출제) → 완료</v>
       </c>
     </row>
     <row r="4">
@@ -5315,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="str">
-        <v>[이월] 숙제 p.34-37 (03.21 출제) → 완료 | [이월] 숙제 p.34-37 (03.17 출제) → 완료</v>
+        <v>[이월] 숙제 p.34-37 (03.17 출제) → 완료</v>
       </c>
     </row>
     <row r="6">
@@ -5529,7 +4614,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="str">
-        <v>[이월] 숙제 p.31-33 (03.17 출제) → 미완료 | [이월] 숙제 p.31-33 (03.17 출제) → 미완료</v>
+        <v>[이월] 숙제 p.31-33 (03.17 출제) → 미완료</v>
       </c>
     </row>
     <row r="6">
